--- a/data/2026/testimonials2026.xlsx
+++ b/data/2026/testimonials2026.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A6AAA-4BDA-497D-B6B1-B9363A22C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA41ED-2A9F-4D36-ADF2-4A3B88259324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Link</t>
   </si>
@@ -47,6 +47,51 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_we-did-it-again-the-registration-for-the-activity-7434543762435043330-myiL?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Jenny Devenport</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/jenny-devenport-b1773b13_the-11th-efspi-regulatory-statistics-workshop-activity-7496444980341788673-WogC?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Looking back on the workshop</t>
+  </si>
+  <si>
+    <t>Looking back on Day 2</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/efspi_efspi-statistics-community-activity-7496446910728278016-w_Xe?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Looking back on Day 1</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/efspi_efspi-statistics-community-activity-7496103516999102464-BuOH?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you to the team </t>
+  </si>
+  <si>
+    <t>Anna Wiksten (EFSPI president)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/efspi_efspi-regulatorystatistics-innovation-activity-7496867044680765440-jH2Q?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Justine Rochon</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/justine-rochon_communication-collaboration-multistakeholder-ugcPost-7496500964053442560-8DQt?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Evgeny Degtyarev</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/ea-fnzZD</t>
+  </si>
+  <si>
+    <t>Pointing out the culture of debate</t>
   </si>
 </sst>
 </file>
@@ -372,14 +417,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="107.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="107.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -390,7 +435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -401,7 +446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -412,28 +457,87 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
     </row>
   </sheetData>

--- a/data/2026/testimonials2026.xlsx
+++ b/data/2026/testimonials2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA41ED-2A9F-4D36-ADF2-4A3B88259324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7602DC-8F5F-4F47-9666-943621DB56B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Link</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>Pointing out the culture of debate</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/eqvd5i5r</t>
   </si>
 </sst>
 </file>
@@ -530,6 +533,9 @@
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
